--- a/reports/dataset_statistics.xlsx
+++ b/reports/dataset_statistics.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="per_class_counts" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="overview" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="per_class_counts" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="overview" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,15 +442,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>AtlasISIC31</t>
+          <t>DermNet</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>DermNet</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>SkinDisNet</t>
         </is>
@@ -463,15 +458,12 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>911</v>
+        <v>779</v>
       </c>
       <c r="C2" t="n">
-        <v>132</v>
+        <v>779</v>
       </c>
       <c r="D2" t="n">
-        <v>779</v>
-      </c>
-      <c r="E2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -482,15 +474,12 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>368</v>
+        <v>236</v>
       </c>
       <c r="C3" t="n">
-        <v>132</v>
+        <v>236</v>
       </c>
       <c r="D3" t="n">
-        <v>236</v>
-      </c>
-      <c r="E3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -501,15 +490,12 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>231</v>
+        <v>103</v>
       </c>
       <c r="C4" t="n">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="D4" t="n">
-        <v>103</v>
-      </c>
-      <c r="E4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -523,12 +509,9 @@
         <v>389</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="D5" t="n">
-        <v>83</v>
-      </c>
-      <c r="E5" t="n">
         <v>306</v>
       </c>
     </row>
@@ -575,7 +558,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3.94</v>
+        <v>7.56</v>
       </c>
     </row>
   </sheetData>

--- a/reports/dataset_statistics.xlsx
+++ b/reports/dataset_statistics.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,10 +442,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>AtlasISIC31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>DermNet</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>SkinDisNet</t>
         </is>
@@ -458,12 +463,15 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>911</v>
+      </c>
+      <c r="C2" t="n">
+        <v>132</v>
+      </c>
+      <c r="D2" t="n">
         <v>779</v>
       </c>
-      <c r="C2" t="n">
-        <v>779</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -474,12 +482,15 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>368</v>
+      </c>
+      <c r="C3" t="n">
+        <v>132</v>
+      </c>
+      <c r="D3" t="n">
         <v>236</v>
       </c>
-      <c r="C3" t="n">
-        <v>236</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -490,12 +501,15 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>231</v>
+      </c>
+      <c r="C4" t="n">
+        <v>128</v>
+      </c>
+      <c r="D4" t="n">
         <v>103</v>
       </c>
-      <c r="C4" t="n">
-        <v>103</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -509,9 +523,12 @@
         <v>389</v>
       </c>
       <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
         <v>83</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>306</v>
       </c>
     </row>
@@ -558,7 +575,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.56</v>
+        <v>3.94</v>
       </c>
     </row>
   </sheetData>
